--- a/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
+++ b/InputData/ccs/BFoCPAbI/BAU Fraction of CCS Potential Achieved by Industry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\BFoCPAbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\BFoCPAbI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52A2814-F7F6-4B4A-87A1-E70FE98E2B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C255099-C710-46E8-8FB3-8FE1851643E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -509,9 +509,6 @@
     <t>Figure 5</t>
   </si>
   <si>
-    <t>Unit: g CO2 captured</t>
-  </si>
-  <si>
     <t>*ethanol mapped to the chemicals industry, ammonia not counted because we assume this industry is decarbonized through the hydrogen PTC</t>
   </si>
   <si>
@@ -1383,6 +1380,9 @@
   </si>
   <si>
     <t>BFoCPAbS BAU Fraction of CCS Potential Achieved by Industry</t>
+  </si>
+  <si>
+    <t>Unit: Dmnl</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2046,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2054,7 +2054,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2087,7 +2087,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2102,22 +2102,22 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2160,12 +2160,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2184,7 +2184,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3546,7 @@
         <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3681,7 +3681,7 @@
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3701,12 +3701,12 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3">
         <v>2021</v>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="38">
         <v>8000000000000</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="38">
         <v>2200000000000</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" s="38">
         <v>33800000000000</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="38">
         <v>0</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B9" s="38">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B10" s="38">
         <v>0</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" s="38">
         <v>0</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B12" s="38">
         <v>2300000000000</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B13" s="38">
         <v>49700000000000</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B14" s="38">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" s="38">
         <v>63800000000000</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B17" s="38">
         <v>36800000000000</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" s="38">
         <v>4400000000000</v>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="38">
         <v>0</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" s="38">
         <v>1007000000</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B21" s="38">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B22" s="38">
         <v>0</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" s="38">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" s="38">
         <v>0</v>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" s="38">
         <v>0</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="38">
         <v>27500000000000</v>
@@ -5986,7 +5986,7 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B28" s="38">
         <v>0</v>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B30">
         <v>2021</v>
@@ -6303,7 +6303,7 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B31" s="38">
         <v>0</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B32" s="38">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B33" s="38">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B34" s="38">
         <v>0</v>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B35" s="38">
         <v>0</v>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B36" s="38">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B37" s="38">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B38" s="38">
         <v>0</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7443,7 +7443,7 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7918,7 +7918,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -8013,7 +8013,7 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -8108,7 +8108,7 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -8488,7 +8488,7 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -8583,7 +8583,7 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -8773,7 +8773,7 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -8868,7 +8868,7 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B58" s="38">
         <v>19502000000</v>
@@ -8963,7 +8963,7 @@
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" s="38">
         <v>2092490000000</v>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B60" s="38">
         <v>11632100000000</v>
@@ -9153,7 +9153,7 @@
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B61" s="38">
         <v>106076000000</v>
@@ -9248,7 +9248,7 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -9343,7 +9343,7 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" s="38">
         <v>5190830000000</v>
@@ -9438,7 +9438,7 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="38">
         <v>2272080000000</v>
@@ -9533,7 +9533,7 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B65" s="38">
         <v>9334890000000</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -9818,7 +9818,7 @@
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="38">
         <v>16366600000000</v>
@@ -9913,7 +9913,7 @@
     </row>
     <row r="69" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="38">
         <v>3431200000000</v>
@@ -10008,7 +10008,7 @@
     </row>
     <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="38">
         <v>91263500000</v>
@@ -10103,7 +10103,7 @@
     </row>
     <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -10198,7 +10198,7 @@
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -10293,7 +10293,7 @@
     </row>
     <row r="73" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -10388,7 +10388,7 @@
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -10483,7 +10483,7 @@
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -10578,7 +10578,7 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -10673,7 +10673,7 @@
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B77" s="38">
         <v>331286000000</v>
@@ -10768,7 +10768,7 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -10863,7 +10863,7 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -11053,7 +11053,7 @@
     </row>
     <row r="81" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B81" s="38">
         <v>4960930000000</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="82" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B82" s="38">
         <v>7932630000000</v>
@@ -11243,7 +11243,7 @@
     </row>
     <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B83" s="38">
         <v>108060000000000</v>
@@ -11338,7 +11338,7 @@
     </row>
     <row r="84" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B84" s="38">
         <v>11110900000000</v>
@@ -11433,7 +11433,7 @@
     </row>
     <row r="85" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B85" s="38">
         <v>48585900000000</v>
@@ -11528,7 +11528,7 @@
     </row>
     <row r="86" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B86" s="38">
         <v>5537710000000</v>
@@ -11623,7 +11623,7 @@
     </row>
     <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B87" s="38">
         <v>3097290000000</v>
@@ -11718,7 +11718,7 @@
     </row>
     <row r="88" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B88" s="38">
         <v>29767700000000</v>
@@ -11813,7 +11813,7 @@
     </row>
     <row r="89" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B89" s="38">
         <v>43963500000000</v>
@@ -11908,7 +11908,7 @@
     </row>
     <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B90" s="38">
         <v>108608000000000</v>
@@ -12003,7 +12003,7 @@
     </row>
     <row r="91" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B91" s="38">
         <v>4303610000000</v>
@@ -12098,7 +12098,7 @@
     </row>
     <row r="92" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B92" s="38">
         <v>5723100000000</v>
@@ -12193,7 +12193,7 @@
     </row>
     <row r="93" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B93" s="38">
         <v>4350300000000</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="94" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B94" s="38">
         <v>0</v>
@@ -12383,7 +12383,7 @@
     </row>
     <row r="95" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B95" s="38">
         <v>10152700000000</v>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="96" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B96" s="38">
         <v>5876500000000</v>
@@ -12573,7 +12573,7 @@
     </row>
     <row r="97" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B97" s="38">
         <v>1637870000000</v>
@@ -12668,7 +12668,7 @@
     </row>
     <row r="98" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B98" s="38">
         <v>1650940000000</v>
@@ -12763,7 +12763,7 @@
     </row>
     <row r="99" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B99" s="38">
         <v>2892370000000</v>
@@ -12858,7 +12858,7 @@
     </row>
     <row r="100" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B100" s="38">
         <v>5139370000000</v>
@@ -12953,7 +12953,7 @@
     </row>
     <row r="101" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B101" s="38">
         <v>2909440000000</v>
@@ -13048,7 +13048,7 @@
     </row>
     <row r="102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B102" s="38">
         <v>17295000000000</v>
@@ -13143,7 +13143,7 @@
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B103" s="38">
         <v>55637100000000</v>
@@ -13238,7 +13238,7 @@
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B104" s="38">
         <v>0</v>
@@ -13333,7 +13333,7 @@
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B105" s="38">
         <v>11695200000000</v>
@@ -13428,7 +13428,7 @@
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B106" s="38">
         <v>0</v>
@@ -13523,7 +13523,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B107" s="38">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B108" s="38">
         <v>0</v>
@@ -13713,7 +13713,7 @@
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -13808,7 +13808,7 @@
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B110" s="38">
         <v>0</v>
@@ -13903,7 +13903,7 @@
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -13998,7 +13998,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B112" s="38">
         <v>0</v>
@@ -14093,7 +14093,7 @@
     </row>
     <row r="113" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B113" s="38">
         <v>0</v>
@@ -14188,7 +14188,7 @@
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B114" s="38">
         <v>0</v>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B115" s="38">
         <v>0</v>
@@ -14378,7 +14378,7 @@
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B116" s="38">
         <v>0</v>
@@ -14473,7 +14473,7 @@
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B117" s="38">
         <v>0</v>
@@ -14568,7 +14568,7 @@
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B118" s="38">
         <v>0</v>
@@ -14663,7 +14663,7 @@
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B119" s="38">
         <v>0</v>
@@ -14758,7 +14758,7 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B120" s="38">
         <v>0</v>
@@ -14853,7 +14853,7 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B121" s="38">
         <v>0</v>
@@ -14948,7 +14948,7 @@
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B122" s="38">
         <v>0</v>
@@ -15043,7 +15043,7 @@
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B123" s="38">
         <v>0</v>
@@ -15138,7 +15138,7 @@
     </row>
     <row r="124" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -15233,7 +15233,7 @@
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -15328,7 +15328,7 @@
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -15423,7 +15423,7 @@
     </row>
     <row r="127" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="128" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="129" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -15708,7 +15708,7 @@
     </row>
     <row r="130" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -15803,7 +15803,7 @@
     </row>
     <row r="131" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B131" s="38">
         <v>35940700000000</v>
@@ -15898,7 +15898,7 @@
     </row>
     <row r="132" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B132" s="38">
         <v>2761920000000</v>
@@ -15993,7 +15993,7 @@
     </row>
     <row r="133" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B133" s="38">
         <v>8379870000000</v>
@@ -16088,7 +16088,7 @@
     </row>
     <row r="134" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B134" s="38">
         <v>8506080000000</v>
@@ -16183,7 +16183,7 @@
     </row>
     <row r="135" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B135" s="38">
         <v>2368720000000</v>
@@ -16278,7 +16278,7 @@
     </row>
     <row r="136" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B136" s="38">
         <v>982499000000</v>
@@ -16373,7 +16373,7 @@
     </row>
     <row r="137" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B137" s="38">
         <v>612997000000</v>
@@ -16468,7 +16468,7 @@
     </row>
     <row r="138" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B138" s="38">
         <v>344397000000</v>
@@ -16563,7 +16563,7 @@
     </row>
     <row r="139" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -16658,7 +16658,7 @@
     </row>
     <row r="140" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B140" s="38">
         <v>85828500000</v>
@@ -16753,7 +16753,7 @@
     </row>
     <row r="141" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -16848,7 +16848,7 @@
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -16943,7 +16943,7 @@
     </row>
     <row r="143" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B143" s="38">
         <v>1625460000000</v>
@@ -17038,7 +17038,7 @@
     </row>
     <row r="144" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B144" s="38">
         <v>309260000000</v>
@@ -17133,7 +17133,7 @@
     </row>
     <row r="145" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B145" s="38">
         <v>922309000000</v>
@@ -17228,7 +17228,7 @@
     </row>
     <row r="146" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -17323,7 +17323,7 @@
     </row>
     <row r="147" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="148" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B148" s="38">
         <v>0</v>
@@ -17513,7 +17513,7 @@
     </row>
     <row r="149" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B149" s="38">
         <v>86011600000</v>
@@ -17608,7 +17608,7 @@
     </row>
     <row r="150" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B150" s="38">
         <v>163681000000</v>
@@ -17703,7 +17703,7 @@
     </row>
     <row r="151" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B151" s="38">
         <v>92660900000</v>
@@ -17798,7 +17798,7 @@
     </row>
     <row r="152" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B152" s="38">
         <v>3068450000000</v>
@@ -17893,7 +17893,7 @@
     </row>
     <row r="153" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B153" s="38">
         <v>0</v>
@@ -17988,7 +17988,7 @@
     </row>
     <row r="154" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B154" s="38">
         <v>0</v>
@@ -18083,7 +18083,7 @@
     </row>
     <row r="155" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B155" s="38">
         <v>44833300000000</v>
@@ -18178,7 +18178,7 @@
     </row>
     <row r="156" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B156" s="38">
         <v>0</v>
@@ -18273,7 +18273,7 @@
     </row>
     <row r="157" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -18368,7 +18368,7 @@
     </row>
     <row r="158" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -18463,7 +18463,7 @@
     </row>
     <row r="159" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -18558,7 +18558,7 @@
     </row>
     <row r="160" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B160" s="38">
         <v>0</v>
@@ -18653,7 +18653,7 @@
     </row>
     <row r="161" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B161" s="38">
         <v>0</v>
@@ -18748,7 +18748,7 @@
     </row>
     <row r="162" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B162" s="38">
         <v>0</v>
@@ -18843,7 +18843,7 @@
     </row>
     <row r="163" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B163" s="38">
         <v>0</v>
@@ -18938,7 +18938,7 @@
     </row>
     <row r="164" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B164" s="38">
         <v>0</v>
@@ -19033,7 +19033,7 @@
     </row>
     <row r="165" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B165" s="38">
         <v>0</v>
@@ -19128,7 +19128,7 @@
     </row>
     <row r="166" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B166" s="38">
         <v>0</v>
@@ -19223,7 +19223,7 @@
     </row>
     <row r="167" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B167" s="38">
         <v>0</v>
@@ -19318,7 +19318,7 @@
     </row>
     <row r="168" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B168" s="38">
         <v>0</v>
@@ -19413,7 +19413,7 @@
     </row>
     <row r="169" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -19508,7 +19508,7 @@
     </row>
     <row r="170" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -19603,7 +19603,7 @@
     </row>
     <row r="171" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -19698,7 +19698,7 @@
     </row>
     <row r="172" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B172" s="38">
         <v>0</v>
@@ -19793,7 +19793,7 @@
     </row>
     <row r="173" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B173" s="38">
         <v>0</v>
@@ -19888,7 +19888,7 @@
     </row>
     <row r="174" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B174" s="38">
         <v>0</v>
@@ -19983,7 +19983,7 @@
     </row>
     <row r="175" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B175" s="38">
         <v>0</v>
@@ -20078,7 +20078,7 @@
     </row>
     <row r="176" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B176" s="38">
         <v>0</v>
@@ -20173,7 +20173,7 @@
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B177" s="38">
         <v>0</v>
@@ -20268,7 +20268,7 @@
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B178" s="38">
         <v>0</v>
@@ -20363,7 +20363,7 @@
     </row>
     <row r="179" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B179" s="38">
         <v>0</v>
@@ -20458,7 +20458,7 @@
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B180" s="38">
         <v>0</v>
@@ -20553,7 +20553,7 @@
     </row>
     <row r="181" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -20648,7 +20648,7 @@
     </row>
     <row r="182" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -20743,7 +20743,7 @@
     </row>
     <row r="183" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B183" s="38">
         <v>0</v>
@@ -20838,7 +20838,7 @@
     </row>
     <row r="184" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -20933,7 +20933,7 @@
     </row>
     <row r="185" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -21028,7 +21028,7 @@
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -21123,7 +21123,7 @@
     </row>
     <row r="187" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -21218,7 +21218,7 @@
     </row>
     <row r="188" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -21313,7 +21313,7 @@
     </row>
     <row r="189" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B189" s="38">
         <v>132433000000000</v>
@@ -21408,7 +21408,7 @@
     </row>
     <row r="190" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -21503,7 +21503,7 @@
     </row>
     <row r="191" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -21598,7 +21598,7 @@
     </row>
     <row r="192" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -21693,7 +21693,7 @@
     </row>
     <row r="193" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -21788,7 +21788,7 @@
     </row>
     <row r="194" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -21883,7 +21883,7 @@
     </row>
     <row r="195" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -21978,7 +21978,7 @@
     </row>
     <row r="196" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B196" s="38">
         <v>0</v>
@@ -22073,7 +22073,7 @@
     </row>
     <row r="197" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -22168,7 +22168,7 @@
     </row>
     <row r="198" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -22263,7 +22263,7 @@
     </row>
     <row r="199" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -22358,7 +22358,7 @@
     </row>
     <row r="200" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -22453,7 +22453,7 @@
     </row>
     <row r="201" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -22548,7 +22548,7 @@
     </row>
     <row r="202" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -22643,7 +22643,7 @@
     </row>
     <row r="203" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -22738,7 +22738,7 @@
     </row>
     <row r="204" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -22833,7 +22833,7 @@
     </row>
     <row r="205" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -22928,7 +22928,7 @@
     </row>
     <row r="206" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B206" s="38">
         <v>16453000000</v>
@@ -23023,7 +23023,7 @@
     </row>
     <row r="207" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B207" s="38">
         <v>59246200000</v>
@@ -23118,7 +23118,7 @@
     </row>
     <row r="208" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B208" s="38">
         <v>322572000000</v>
@@ -23213,7 +23213,7 @@
     </row>
     <row r="209" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -23308,7 +23308,7 @@
     </row>
     <row r="210" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B210" s="38">
         <v>28550500000</v>
@@ -23403,7 +23403,7 @@
     </row>
     <row r="211" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B211" s="38">
         <v>14411100000</v>
@@ -23498,7 +23498,7 @@
     </row>
     <row r="212" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B212">
         <v>0</v>
@@ -23593,7 +23593,7 @@
     </row>
     <row r="213" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B213" s="38">
         <v>2067700000000</v>
@@ -23688,7 +23688,7 @@
     </row>
     <row r="214" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B214">
         <v>0</v>
@@ -23783,7 +23783,7 @@
     </row>
     <row r="215" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B215" s="38">
         <v>263361000000</v>
@@ -23878,7 +23878,7 @@
     </row>
     <row r="216" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B216" s="38">
         <v>8486300</v>
@@ -23973,7 +23973,7 @@
     </row>
     <row r="217" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B217">
         <v>0</v>
@@ -24068,7 +24068,7 @@
     </row>
     <row r="218" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B218">
         <v>0</v>
@@ -24163,7 +24163,7 @@
     </row>
     <row r="219" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -24258,7 +24258,7 @@
     </row>
     <row r="220" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B220" s="38">
         <v>12398800000</v>
@@ -24353,7 +24353,7 @@
     </row>
     <row r="221" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B221" s="38">
         <v>393749000</v>
@@ -24448,7 +24448,7 @@
     </row>
     <row r="222" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B222" s="38">
         <v>3679900</v>
@@ -24543,7 +24543,7 @@
     </row>
     <row r="223" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B223">
         <v>0</v>
@@ -24638,7 +24638,7 @@
     </row>
     <row r="224" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B224" s="38">
         <v>21628800</v>
@@ -24733,7 +24733,7 @@
     </row>
     <row r="225" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B225" s="38">
         <v>178015000000</v>
@@ -24828,7 +24828,7 @@
     </row>
     <row r="226" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B226" s="38">
         <v>100776000000</v>
@@ -24923,7 +24923,7 @@
     </row>
     <row r="227" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B227" s="38">
         <v>45007600000</v>
@@ -25018,7 +25018,7 @@
     </row>
     <row r="228" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -25113,7 +25113,7 @@
     </row>
     <row r="229" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -25208,7 +25208,7 @@
     </row>
     <row r="230" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -25303,7 +25303,7 @@
     </row>
     <row r="231" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B231" s="38">
         <v>5608430000000</v>
@@ -25398,7 +25398,7 @@
     </row>
     <row r="232" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -25493,7 +25493,7 @@
     </row>
     <row r="233" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -25588,7 +25588,7 @@
     </row>
     <row r="234" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -25683,7 +25683,7 @@
     </row>
     <row r="235" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B235" s="38">
         <v>257088000000</v>
@@ -25778,7 +25778,7 @@
     </row>
     <row r="236" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B236" s="38">
         <v>61737800000</v>
@@ -25873,7 +25873,7 @@
     </row>
     <row r="237" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B237" s="38">
         <v>96430100000</v>
@@ -25968,7 +25968,7 @@
     </row>
     <row r="238" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B238" s="38">
         <v>35762800000</v>
@@ -26063,7 +26063,7 @@
     </row>
     <row r="239" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -26158,7 +26158,7 @@
     </row>
     <row r="240" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -26253,7 +26253,7 @@
     </row>
     <row r="241" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B241" s="38">
         <v>63824400000</v>
@@ -26348,7 +26348,7 @@
     </row>
     <row r="242" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -26443,7 +26443,7 @@
     </row>
     <row r="243" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -26538,7 +26538,7 @@
     </row>
     <row r="244" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -26633,7 +26633,7 @@
     </row>
     <row r="245" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B245" s="38">
         <v>53116700000</v>
@@ -26728,7 +26728,7 @@
     </row>
     <row r="246" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B246" s="38">
         <v>62027300000</v>
@@ -26823,7 +26823,7 @@
     </row>
     <row r="247" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -26918,7 +26918,7 @@
     </row>
     <row r="248" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B248" s="38">
         <v>30892700000</v>
@@ -27013,7 +27013,7 @@
     </row>
     <row r="249" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B249" s="38">
         <v>31605100000</v>
@@ -27108,7 +27108,7 @@
     </row>
     <row r="250" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B250" s="38">
         <v>39774100000</v>
@@ -27203,7 +27203,7 @@
     </row>
     <row r="251" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B251" s="38">
         <v>22516500000</v>
@@ -27298,7 +27298,7 @@
     </row>
     <row r="252" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B252" s="38">
         <v>192814000000</v>
@@ -27393,7 +27393,7 @@
     </row>
     <row r="253" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -27488,7 +27488,7 @@
     </row>
     <row r="254" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -27583,7 +27583,7 @@
     </row>
     <row r="255" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B255" s="38">
         <v>1626140000000</v>
@@ -27678,7 +27678,7 @@
     </row>
     <row r="256" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -27773,7 +27773,7 @@
     </row>
     <row r="257" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B257" s="38">
         <v>0</v>
@@ -27868,7 +27868,7 @@
     </row>
     <row r="258" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B258" s="38">
         <v>0</v>
@@ -27963,7 +27963,7 @@
     </row>
     <row r="259" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B259" s="38">
         <v>0</v>
@@ -28058,7 +28058,7 @@
     </row>
     <row r="260" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B260" s="38">
         <v>0</v>
@@ -28153,7 +28153,7 @@
     </row>
     <row r="261" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B261" s="38">
         <v>0</v>
@@ -28248,7 +28248,7 @@
     </row>
     <row r="262" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B262" s="38">
         <v>0</v>
@@ -28343,7 +28343,7 @@
     </row>
     <row r="263" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B263" s="38">
         <v>0</v>
@@ -28438,7 +28438,7 @@
     </row>
     <row r="264" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B264" s="38">
         <v>0</v>
@@ -28533,7 +28533,7 @@
     </row>
     <row r="265" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -28628,7 +28628,7 @@
     </row>
     <row r="266" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B266" s="38">
         <v>0</v>
@@ -28723,7 +28723,7 @@
     </row>
     <row r="267" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -28818,7 +28818,7 @@
     </row>
     <row r="268" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B268" s="38">
         <v>0</v>
@@ -28913,7 +28913,7 @@
     </row>
     <row r="269" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B269" s="38">
         <v>0</v>
@@ -29008,7 +29008,7 @@
     </row>
     <row r="270" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B270" s="38">
         <v>0</v>
@@ -29103,7 +29103,7 @@
     </row>
     <row r="271" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B271" s="38">
         <v>0</v>
@@ -29198,7 +29198,7 @@
     </row>
     <row r="272" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B272" s="38">
         <v>0</v>
@@ -29293,7 +29293,7 @@
     </row>
     <row r="273" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B273" s="38">
         <v>0</v>
@@ -29388,7 +29388,7 @@
     </row>
     <row r="274" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B274" s="38">
         <v>0</v>
@@ -29483,7 +29483,7 @@
     </row>
     <row r="275" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B275" s="38">
         <v>0</v>
@@ -29578,7 +29578,7 @@
     </row>
     <row r="276" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B276" s="38">
         <v>0</v>
@@ -29673,7 +29673,7 @@
     </row>
     <row r="277" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B277" s="38">
         <v>0</v>
@@ -29768,7 +29768,7 @@
     </row>
     <row r="278" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -29863,7 +29863,7 @@
     </row>
     <row r="279" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -29958,7 +29958,7 @@
     </row>
     <row r="280" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -30085,7 +30085,7 @@
     </row>
     <row r="282" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B282" s="38">
         <f>SUM(B39,B64,B89,B114,B139,B164,B189,B214,B239,B264)</f>
@@ -30739,7 +30739,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>157</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1">
         <v>2021</v>
@@ -33258,7 +33258,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>157</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1">
         <v>2021</v>
